--- a/results/05_transient_transcription_output/209/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/209/Top_Excel_with_OCR_Results.xlsx
@@ -626,128 +626,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">437
-</t>
+          <t>437</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">637
-</t>
+          <t>637</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="X4" s="2" t="n"/>
@@ -772,135 +751,113 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
-</t>
+          <t>878</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">741
-</t>
+          <t>741</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -922,140 +879,117 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1006
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
-</t>
+          <t>886</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
-</t>
+          <t>619</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1072,141 +1006,118 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">437
-</t>
+          <t>437</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
-</t>
+          <t>330</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8726
-</t>
+          <t>876</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1521
-</t>
+          <t>521</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">779
-</t>
+          <t>779</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
-</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1223,14 +1134,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
-</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1240,128 +1149,107 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">877
-</t>
+          <t>877</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">954
-</t>
+          <t>954</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1752
-</t>
+          <t>752</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1378,146 +1266,122 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1666
-</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8526
-</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
-</t>
+          <t>925</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8225
-</t>
+          <t>1225</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
-</t>
+          <t>805</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
-</t>
+          <t>442</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
-</t>
+          <t>943</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
-</t>
+          <t>878</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">963
-</t>
+          <t>963</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4409
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1388
-</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16173
-</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1319
-</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3609
-</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">585
-</t>
+          <t>585</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
-</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
-</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1295
-</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4024
-</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1534,146 +1398,122 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
+          <t>333</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1876
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
+          <t>882</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
-</t>
+          <t>722</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
-</t>
+          <t>805</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1690,104 +1530,87 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">445
-</t>
+          <t>445</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
-</t>
+          <t>879</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1797,20 +1620,17 @@
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
@@ -1820,14 +1640,12 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
-</t>
+          <t>975</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1844,140 +1662,117 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">383
-</t>
+          <t>383</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
-</t>
+          <t>884</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
-</t>
+          <t>854</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11977
-</t>
+          <t>977</t>
         </is>
       </c>
       <c r="Z12" s="2" t="n"/>
@@ -1995,146 +1790,122 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2356
-</t>
+          <t>356</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
-</t>
+          <t>891</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
-</t>
+          <t>327</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
-</t>
+          <t>836</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
-</t>
+          <t>929</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2151,134 +1922,112 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">374
-</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
-</t>
+          <t>325</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
+          <t>899</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">509
-</t>
+          <t>509</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -2288,8 +2037,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2306,146 +2054,122 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1433
-</t>
+          <t>433</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">638
-</t>
+          <t>638</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2462,26 +2186,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19928
-</t>
+          <t>19926</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1499
-</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
-</t>
+          <t>991</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
-</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2491,20 +2211,17 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
@@ -2515,68 +2232,57 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1946
-</t>
+          <t>946</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1052
-</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4441
-</t>
+          <t>4441</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
-</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
-</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10425
-</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3687
-</t>
+          <t>3687</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">531
-</t>
+          <t>531</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
-</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
-</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
@@ -2586,14 +2292,12 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4551
-</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2610,146 +2314,122 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3998
-</t>
+          <t>398</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115515
-</t>
+          <t>011</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1737
-</t>
+          <t>737</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2771,38 +2451,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2812,98 +2486,82 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">631
-</t>
+          <t>631</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
-</t>
+          <t>921</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2920,140 +2578,117 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22234
-</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
-</t>
+          <t>325</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
-</t>
+          <t>875</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">540
-</t>
+          <t>540</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>812</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -3080,140 +2715,117 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12415
-</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">707
-</t>
+          <t>707</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">672
-</t>
+          <t>672</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3230,146 +2842,122 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">433
-</t>
+          <t>433</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">867
-</t>
+          <t>867</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3386,32 +2974,27 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23746
-</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12475
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -3421,110 +3004,92 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
-</t>
+          <t>302</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2564
-</t>
+          <t>564</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
-</t>
+          <t>855</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3541,110 +3106,92 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1925
-</t>
+          <t>19255</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
-</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
-</t>
+          <t>928</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
-</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
-</t>
+          <t>603</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">495
-</t>
+          <t>492</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
-</t>
+          <t>952</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
+          <t>882</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
-</t>
+          <t>965</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4372
-</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1462
-</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
-</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28952
-</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3654,32 +3201,27 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
-</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
-</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
-</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4110
-</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3696,146 +3238,122 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13985
-</t>
+          <t>385</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1676
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>874</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>822</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3852,38 +3370,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23740
-</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3893,104 +3405,87 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
-</t>
+          <t>569</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1748
-</t>
+          <t>748</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -4007,146 +3502,122 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3298
-</t>
+          <t>3298</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
+          <t>800</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4163,8 +3634,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13544
-</t>
+          <t>3548</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -4174,122 +3644,102 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>875</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
-</t>
+          <t>684</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
@@ -4299,8 +3749,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4317,140 +3766,117 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3893
-</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>874</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">649
-</t>
+          <t>649</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
+          <t>820</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -4472,146 +3898,122 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>408</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>294</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
-</t>
+          <t>626</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4628,14 +4030,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18564
-</t>
+          <t>18564</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1503
-</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -4645,128 +4045,107 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
-</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1525
-</t>
+          <t>525</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1917
-</t>
+          <t>913</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>296</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
-</t>
+          <t>932</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1032
-</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419
-</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1385
-</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
-</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3328
-</t>
+          <t>3328</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
-</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
-</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
-</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3998
-</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4783,146 +4162,122 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">371
-</t>
+          <t>371</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
-</t>
+          <t>884</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
-</t>
+          <t>666</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
+          <t>800</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4939,80 +4294,67 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">457
-</t>
+          <t>437</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13528
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1669
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
-</t>
+          <t>884</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -5022,62 +4364,52 @@
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">566
-</t>
+          <t>566</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -5094,38 +4426,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3979
-</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">337
-</t>
+          <t>337</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -5135,104 +4461,87 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>874</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
+          <t>329</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1477
-</t>
+          <t>477</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">776
-</t>
+          <t>776</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5249,146 +4558,122 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13624
-</t>
+          <t>3624</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">873
-</t>
+          <t>873</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">786
-</t>
+          <t>786</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>832</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5405,146 +4690,122 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
-</t>
+          <t>879</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
-</t>
+          <t>854</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5561,140 +4822,117 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3989
-</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
-</t>
+          <t>723</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">782
-</t>
+          <t>782</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -5716,146 +4954,122 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1683
-</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1501
-</t>
+          <t>1501</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1009
-</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
-</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1492
-</t>
+          <t>492</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
-</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1028
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1035
-</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
-</t>
+          <t>965</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1072
-</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4375
-</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1396
-</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
-</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
-</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3437
-</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">657
-</t>
+          <t>657</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
-</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
-</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1271
-</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3966
-</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
-</t>
+          <t>344</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5872,146 +5086,122 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23267
-</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
-</t>
+          <t>875</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">687
-</t>
+          <t>687</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">793
-</t>
+          <t>793</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -6028,146 +5218,122 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14008
-</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
-</t>
+          <t>545</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">784
-</t>
+          <t>784</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -6184,146 +5350,122 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">744
-</t>
+          <t>744</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2841
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1221
-</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11290
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
-</t>
+          <t>897</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
-</t>
+          <t>855</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">813
-</t>
+          <t>813</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6340,146 +5482,122 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2448
-</t>
+          <t>4482</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>294</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
-</t>
+          <t>891</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">584
-</t>
+          <t>574</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6496,146 +5614,122 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1500
-</t>
+          <t>500</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6652,128 +5746,107 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23413
-</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>320</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1881
-</t>
+          <t>881</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
+          <t>814</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
@@ -6783,14 +5856,12 @@
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
-</t>
+          <t>828</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6807,74 +5878,62 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416
-</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2041
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -6884,50 +5943,42 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="X44" s="2" t="n"/>
@@ -6952,68 +6003,57 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740
-</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1440
-</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">602
-</t>
+          <t>602</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1056
-</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
-</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1092
-</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12181
-</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -7023,63 +6063,53 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1404
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1575
-</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1297
-</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1385
-</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4240
-</t>
+          <t>4140</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11215
-</t>
+          <t>715</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1455
-</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2312
-</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="X45" s="2" t="n"/>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">483904
-</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -7096,129 +6126,112 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3117
-</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1041
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11676
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
-</t>
+          <t>690</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="Y46" s="2" t="n"/>
